--- a/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/sszw_vorlage.xlsx
+++ b/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/sszw_vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eclipse\PlanPro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_intern\planpro\set\java\bundles\org.eclipse.set.feature\rootdir\data\export\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996FCCA4-D6E1-4B8E-8504-74DCC5FEEE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E568BDB-A37A-4C33-8BBA-8F5926811CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sszw_Beispielbefüllung" sheetId="2" r:id="rId1"/>
@@ -475,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -540,13 +540,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -555,10 +549,13 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -585,11 +582,32 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -965,19 +983,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="16" customWidth="1"/>
     <col min="2" max="2" width="10" style="16" customWidth="1"/>
-    <col min="3" max="3" width="4.77734375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="16" customWidth="1"/>
     <col min="5" max="14" width="10" style="16" customWidth="1"/>
     <col min="15" max="15" width="10" style="20" customWidth="1"/>
-    <col min="16" max="16" width="35.109375" style="16" customWidth="1"/>
-    <col min="17" max="16384" width="10.88671875" style="16"/>
+    <col min="16" max="16" width="35.140625" style="16" customWidth="1"/>
+    <col min="17" max="16384" width="10.85546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1024,69 +1042,69 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="29" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="29" t="s">
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="30"/>
-      <c r="O2" s="37" t="s">
+      <c r="N2" s="29"/>
+      <c r="O2" s="26" t="s">
         <v>34</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="32" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="33"/>
-      <c r="G3" s="34" t="s">
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="36" t="s">
+      <c r="H3" s="34"/>
+      <c r="I3" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34" t="s">
+      <c r="J3" s="33"/>
+      <c r="K3" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="35"/>
+      <c r="L3" s="34"/>
       <c r="M3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="28" t="s">
+      <c r="N3" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="38"/>
+      <c r="O3" s="27"/>
       <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
@@ -1121,10 +1139,10 @@
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="8"/>
-      <c r="O4" s="38"/>
+      <c r="O4" s="27"/>
       <c r="P4" s="18"/>
     </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
@@ -1154,37 +1172,39 @@
       <c r="O5" s="19"/>
       <c r="P5" s="19"/>
     </row>
-    <row r="6" spans="1:16" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="44"/>
     </row>
-    <row r="7" spans="1:16" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="25"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="25"/>
+    <row r="7" spans="1:16" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1205,6 +1225,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100E758A0F93049BE4CAD441F10C0D8186D" ma:contentTypeVersion="5" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="fb340e34ecc5d059b634082484788e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="576ce185-3b2e-4f75-8b7c-efeb82226bea" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v3/fields" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae5cd419a40dc0c21009e0c04d2bd83e" ns2:_="" ns3:_="">
     <xsd:import namespace="576ce185-3b2e-4f75-8b7c-efeb82226bea"/>
@@ -1396,20 +1425,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -1455,7 +1471,19 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF743650-405A-4EB5-9BE5-79180E38FBC9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B642628-E0AC-4F61-AC13-56E3126AE48A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1474,26 +1502,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF743650-405A-4EB5-9BE5-79180E38FBC9}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9CFCEAE-5A31-4E8D-871E-0FEB90E546B0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AA9053-CA78-458B-BFEC-B0A103F9F68C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9CFCEAE-5A31-4E8D-871E-0FEB90E546B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>